--- a/CompssaStudents/COMPSSA BDS LIST.xlsx
+++ b/CompssaStudents/COMPSSA BDS LIST.xlsx
@@ -1,119 +1,111 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19368" windowHeight="9780"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="199">
-  <si>
-    <t>Ajayi Adebayo David</t>
-  </si>
-  <si>
-    <t>NDUKASTPAUL ELISHAMA ONENGIYEOFORI</t>
-  </si>
-  <si>
-    <t>Mohammed Sulaiman Musa</t>
-  </si>
-  <si>
-    <t>Rahman Aleemah Ibukunoluwa</t>
-  </si>
-  <si>
-    <t>Masha David Chukwuemeka</t>
-  </si>
-  <si>
-    <t>Chiwetalu Daphne Obiajulum</t>
-  </si>
-  <si>
-    <t>Olawoyin Olubukola Tabitha</t>
-  </si>
-  <si>
-    <t>Omikunle Olamide Eniola</t>
-  </si>
-  <si>
-    <t>Kazeem Idris Opeyemi</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+  <si>
+    <t xml:space="preserve">Ajayi Adebayo David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUKASTPAUL ELISHAMA ONENGIYEOFORI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohammed Sulaiman Musa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rahman Aleemah Ibukunoluwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masha David Chukwuemeka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiwetalu Daphne Obiajulum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olawoyin Olubukola Tabitha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omikunle Olamide Eniola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazeem Idris Opeyemi</t>
   </si>
   <si>
     <t xml:space="preserve">Omotola Bashorun </t>
   </si>
   <si>
-    <t>Okoro Elizabeth Ezenwanyi</t>
-  </si>
-  <si>
-    <t>Adeboyejo Abdulateef Abolaji</t>
-  </si>
-  <si>
-    <t>Kehinde Joy Moyoninuoluwa</t>
-  </si>
-  <si>
-    <t>Olaolu Oreoluwa Aliya</t>
-  </si>
-  <si>
-    <t>Adobu Jennifer Emoshogwe</t>
-  </si>
-  <si>
-    <t>Fasaye Jolaade Fridaws</t>
-  </si>
-  <si>
-    <t>Amosun Iradatullahi Adetutu.</t>
-  </si>
-  <si>
-    <t>Joshua Victor Damilola</t>
-  </si>
-  <si>
-    <t>Kappo Ayomide Chiamaka</t>
-  </si>
-  <si>
-    <t>Muhammed Barakat Omowonuola</t>
-  </si>
-  <si>
-    <t>Aminah Adeola Raheem</t>
-  </si>
-  <si>
-    <t>Oraegbu Ebube Olive</t>
-  </si>
-  <si>
-    <t>Ugorji Joshua Ayomide</t>
-  </si>
-  <si>
-    <t>Abdulazeez Aishat Olasumbo</t>
-  </si>
-  <si>
-    <t>Kolawole Nurat Temitope</t>
-  </si>
-  <si>
-    <t>Oriade Michael Olatomide</t>
-  </si>
-  <si>
-    <t>Sheidu Oluwadamilola Victoria</t>
-  </si>
-  <si>
-    <t>Lawal Aisha Olasubomi</t>
-  </si>
-  <si>
-    <t>Sogbesan Olamiposi Adelani</t>
-  </si>
-  <si>
-    <t>Adefemi Eunice Omolayo</t>
+    <t xml:space="preserve">Okoro Elizabeth Ezenwanyi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adeboyejo Abdulateef Abolaji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kehinde Joy Moyoninuoluwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olaolu Oreoluwa Aliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adobu Jennifer Emoshogwe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fasaye Jolaade Fridaws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amosun Iradatullahi Adetutu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joshua Victor Damilola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kappo Ayomide Chiamaka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muhammed Barakat Omowonuola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aminah Adeola Raheem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oraegbu Ebube Olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ugorji Joshua Ayomide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdulazeez Aishat Olasumbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolawole Nurat Temitope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriade Michael Olatomide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheidu Oluwadamilola Victoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawal Aisha Olasubomi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sogbesan Olamiposi Adelani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adefemi Eunice Omolayo</t>
   </si>
   <si>
     <t xml:space="preserve">Abiodun Mariah </t>
@@ -122,244 +114,244 @@
     <t xml:space="preserve">Balogun Hazeezah </t>
   </si>
   <si>
-    <t>Odekunle David Oluwarotimi</t>
+    <t xml:space="preserve">Odekunle David Oluwarotimi</t>
   </si>
   <si>
     <t xml:space="preserve">Akpovofene Larson </t>
   </si>
   <si>
-    <t>Omale Racheal Ojonago</t>
+    <t xml:space="preserve">Omale Racheal Ojonago</t>
   </si>
   <si>
     <t xml:space="preserve">Ajayi Solomon </t>
   </si>
   <si>
-    <t>Owolabi Olarinsade Rhoda</t>
-  </si>
-  <si>
-    <t>ISIEKWE Victoria Chukwudalu</t>
-  </si>
-  <si>
-    <t>Nzekwe Chizurumoke Faithwin</t>
-  </si>
-  <si>
-    <t>Kayode Precious Omowunmi</t>
-  </si>
-  <si>
-    <t>Famuyiwa Oluwamayowa Oyinkansola</t>
+    <t xml:space="preserve">Owolabi Olarinsade Rhoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISIEKWE Victoria Chukwudalu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nzekwe Chizurumoke Faithwin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayode Precious Omowunmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Famuyiwa Oluwamayowa Oyinkansola</t>
   </si>
   <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
-    <t>Ajulo Thomas Oluwashinaayomi</t>
-  </si>
-  <si>
-    <t>Popoola Aishat Ayomide</t>
-  </si>
-  <si>
-    <t>Matti Fawas Ayomide</t>
-  </si>
-  <si>
-    <t>Oyegoke Tumilara Testimony</t>
-  </si>
-  <si>
-    <t>Adekunle Ajoke Fathiat</t>
-  </si>
-  <si>
-    <t>Andrew Emmanuel Ogirima</t>
-  </si>
-  <si>
-    <t>Orekoya Oluwasegun David</t>
-  </si>
-  <si>
-    <t>Abdulquadri Saheed Alani</t>
-  </si>
-  <si>
-    <t>Talabi Abdulquareeb Babatunde</t>
-  </si>
-  <si>
-    <t>Oluwatade Emmanuel Oluwatobiloba</t>
-  </si>
-  <si>
-    <t>Titilola Aderinsola Medinat</t>
-  </si>
-  <si>
-    <t>Ariyo Victoria Bisola</t>
-  </si>
-  <si>
-    <t>Oladipupo Kehinde Sarah</t>
-  </si>
-  <si>
-    <t>Ukpai Ucha Chinyere</t>
-  </si>
-  <si>
-    <t>Olagunju Asiyah Modupeola</t>
-  </si>
-  <si>
-    <t>Ibitoye Nifemi Emmanuel</t>
-  </si>
-  <si>
-    <t>Adenuga Joshua Timilehin</t>
-  </si>
-  <si>
-    <t>Adebamigbe Queen Ifeoluwa</t>
-  </si>
-  <si>
-    <t>Olumodeji Blessing Fadesewa</t>
-  </si>
-  <si>
-    <t>Chinweuba-Onoh Ebube Favour</t>
-  </si>
-  <si>
-    <t>Ntan Jemimah Ese</t>
-  </si>
-  <si>
-    <t>Adeyemi Kausarat Oladunni</t>
+    <t xml:space="preserve">30 LEVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajulo Thomas Oluwashinaayomi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popoola Aishat Ayomide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matti Fawas Ayomide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oyegoke Tumilara Testimony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adekunle Ajoke Fathiat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Emmanuel Ogirima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orekoya Oluwasegun David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdulquadri Saheed Alani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talabi Abdulquareeb Babatunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oluwatade Emmanuel Oluwatobiloba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titilola Aderinsola Medinat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ariyo Victoria Bisola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oladipupo Kehinde Sarah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukpai Ucha Chinyere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olagunju Asiyah Modupeola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibitoye Nifemi Emmanuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adenuga Joshua Timilehin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adebamigbe Queen Ifeoluwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olumodeji Blessing Fadesewa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chinweuba-Onoh Ebube Favour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ntan Jemimah Ese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adeyemi Kausarat Oladunni</t>
   </si>
   <si>
     <t xml:space="preserve">Adeyoyomoye Aduragbemi </t>
   </si>
   <si>
-    <t>Adeeko Michael Oladimeji</t>
-  </si>
-  <si>
-    <t>Diekola Abdulazeez Aramide</t>
-  </si>
-  <si>
-    <t>Akinlabi Ebunoluwa Elizabeth</t>
-  </si>
-  <si>
-    <t>Nikoro Oreofe Oluwatumininu</t>
-  </si>
-  <si>
-    <t>Mohammed Sofiyyah Ajoke</t>
-  </si>
-  <si>
-    <t>Odulukwe Raphael Chimaobim</t>
-  </si>
-  <si>
-    <t>Ohaegbu Isioma Gabriella</t>
-  </si>
-  <si>
-    <t>Ogbodu Ogheneochuko Mofoluwake</t>
-  </si>
-  <si>
-    <t>Ezeji Favour Ebubechukwu</t>
-  </si>
-  <si>
-    <t>Ume Sarah Kosisochukwu</t>
-  </si>
-  <si>
-    <t>Akorede Sururat Kofoworola</t>
-  </si>
-  <si>
-    <t>Daramola Binta Omotola</t>
-  </si>
-  <si>
-    <t>Muibi Rodiat Opeyemi</t>
-  </si>
-  <si>
-    <t>Oduleye Oreoluwa Oluwafunmilayo</t>
-  </si>
-  <si>
-    <t>Etibeng Glorious Ernest</t>
-  </si>
-  <si>
-    <t>Emmanuel Chidinma Vivian</t>
-  </si>
-  <si>
-    <t>Maxwell Favour Chinenye</t>
-  </si>
-  <si>
-    <t>Anorue Emmanuella Nneoma</t>
+    <t xml:space="preserve">Adeeko Michael Oladimeji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diekola Abdulazeez Aramide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akinlabi Ebunoluwa Elizabeth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nikoro Oreofe Oluwatumininu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohammed Sofiyyah Ajoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odulukwe Raphael Chimaobim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohaegbu Isioma Gabriella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogbodu Ogheneochuko Mofoluwake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezeji Favour Ebubechukwu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ume Sarah Kosisochukwu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akorede Sururat Kofoworola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daramola Binta Omotola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muibi Rodiat Opeyemi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oduleye Oreoluwa Oluwafunmilayo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etibeng Glorious Ernest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emmanuel Chidinma Vivian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maxwell Favour Chinenye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anorue Emmanuella Nneoma</t>
   </si>
   <si>
     <t xml:space="preserve">Abass Abdullah </t>
   </si>
   <si>
-    <t>30 LEVEL</t>
-  </si>
-  <si>
-    <t>Brown Sophia Ibiene</t>
-  </si>
-  <si>
-    <t>Olalekan Adedamola Joshua</t>
-  </si>
-  <si>
-    <t>Afolayan Jeremiah Adebayo</t>
-  </si>
-  <si>
-    <t>Aremo Anjolaoluwa Mosunmola</t>
-  </si>
-  <si>
-    <t>Raji Arafat Ajedolapo</t>
-  </si>
-  <si>
-    <t>Oluwadare Iyanu Silvanus</t>
-  </si>
-  <si>
-    <t>Ibitoye Eniola Racheal</t>
-  </si>
-  <si>
-    <t>Ojo Peter Oluwamayowa</t>
-  </si>
-  <si>
-    <t>Yussuf Al-ameen Olamilekan</t>
-  </si>
-  <si>
-    <t>Olowo Favour Ayoola</t>
-  </si>
-  <si>
-    <t>Ahoua Blessing Ebunola</t>
-  </si>
-  <si>
-    <t>Otori Deborah Ohunene</t>
-  </si>
-  <si>
-    <t>Dahunsi Samuel Ayodeji</t>
-  </si>
-  <si>
-    <t>Ogunlana Fathia Opeyemi</t>
-  </si>
-  <si>
-    <t>Onyedikachi David Adewale</t>
-  </si>
-  <si>
-    <t>Ogunrinde Ifeoluwalademi Joy</t>
-  </si>
-  <si>
-    <t>Bankole Busayo Okunola</t>
-  </si>
-  <si>
-    <t>Abdus-salam Sameedah Doyinsola</t>
-  </si>
-  <si>
-    <t>Yakub Yusuf Ayomide</t>
-  </si>
-  <si>
-    <t>Alabi Ayomide Ayodeji</t>
-  </si>
-  <si>
-    <t>Adebowale Moradeyo Mariam</t>
-  </si>
-  <si>
-    <t>Ajiboye Ibukunoluwa Oluchi</t>
-  </si>
-  <si>
-    <t>Adebayo Kenneth Ayodele</t>
-  </si>
-  <si>
-    <t>Owabumowa Iyitoni Elizabeth</t>
-  </si>
-  <si>
-    <t>Ojelade Mubarak Bolarinwa</t>
-  </si>
-  <si>
-    <t>Adenekan Oluwadarasimi Oluwasemilogo</t>
-  </si>
-  <si>
-    <t>Oyebade Mercy Oluwadunmininu</t>
+    <t xml:space="preserve">Brown Sophia Ibiene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olalekan Adedamola Joshua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afolayan Jeremiah Adebayo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aremo Anjolaoluwa Mosunmola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raji Arafat Ajedolapo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oluwadare Iyanu Silvanus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibitoye Eniola Racheal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ojo Peter Oluwamayowa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yussuf Al-ameen Olamilekan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olowo Favour Ayoola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoua Blessing Ebunola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otori Deborah Ohunene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dahunsi Samuel Ayodeji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogunlana Fathia Opeyemi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onyedikachi David Adewale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogunrinde Ifeoluwalademi Joy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bankole Busayo Okunola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdus-salam Sameedah Doyinsola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yakub Yusuf Ayomide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alabi Ayomide Ayodeji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adebowale Moradeyo Mariam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajiboye Ibukunoluwa Oluchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adebayo Kenneth Ayodele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owabumowa Iyitoni Elizabeth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ojelade Mubarak Bolarinwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adenekan Oluwadarasimi Oluwasemilogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oyebade Mercy Oluwadunmininu</t>
   </si>
   <si>
     <t xml:space="preserve">OniAkorede Zion </t>
@@ -368,271 +360,270 @@
     <t xml:space="preserve">Simone-Marie Chukwu </t>
   </si>
   <si>
-    <t>Adelusi Ifeoluwa Grace-Anu</t>
+    <t xml:space="preserve">Adelusi Ifeoluwa Grace-Anu</t>
   </si>
   <si>
     <t xml:space="preserve">Oyeneye SofiahYoyinsola </t>
   </si>
   <si>
-    <t>Adeniyi Muinat Omobusayo</t>
-  </si>
-  <si>
-    <t>Obiwulu God'swill Eric</t>
-  </si>
-  <si>
-    <t>Teniola Eniola Naomi</t>
-  </si>
-  <si>
-    <t>Raji Khairat Ayomide</t>
-  </si>
-  <si>
-    <t>Adeyeye Folasade Blessing</t>
-  </si>
-  <si>
-    <t>Opreh Victor Omoghene</t>
-  </si>
-  <si>
-    <t>Bazuaye Peter Esosa</t>
-  </si>
-  <si>
-    <t>Obiwulu Josephine Amarachi</t>
-  </si>
-  <si>
-    <t>Anoma Onyinyechukwu Daniella</t>
-  </si>
-  <si>
-    <t>Gladstone Okechukwu Nnabue</t>
-  </si>
-  <si>
-    <t>Robert Endurance Ehidiame</t>
-  </si>
-  <si>
-    <t>Ofili Great Echendu</t>
-  </si>
-  <si>
-    <t>IBANGA, ABASIONO NSIKANABASI</t>
-  </si>
-  <si>
-    <t>Adigwu, Judith Ogechukwu</t>
-  </si>
-  <si>
-    <t>Ago, Henry Boniface</t>
-  </si>
-  <si>
-    <t>Ajekwe, Elizabeth Yaveren</t>
-  </si>
-  <si>
-    <t>Akin-ologunowa, Oluwadamilola Peace</t>
-  </si>
-  <si>
-    <t>Akomaye, Emmanuella Agiounim</t>
-  </si>
-  <si>
-    <t>Asuquo, Deborah Asuquo</t>
-  </si>
-  <si>
-    <t>Awafung, Rosemary Odey</t>
-  </si>
-  <si>
-    <t>Eyo, Gideon Edet</t>
-  </si>
-  <si>
-    <t>Owolabi, Confidence Tolulope</t>
-  </si>
-  <si>
-    <t>ANIGBEDU EVIDENCE DAVID</t>
-  </si>
-  <si>
-    <t>ALUMMA CHIDERA JESSICA</t>
-  </si>
-  <si>
-    <t>NICHOLAS NAOMI BLESSING</t>
-  </si>
-  <si>
-    <t>AKHIGBE OSIREGBEMHE EMMANUEL</t>
-  </si>
-  <si>
-    <t>IBITOYE TIMILEHIN ISRAEL</t>
-  </si>
-  <si>
-    <t>OKUYIGA ADEDAYO OLUWAROTIMI</t>
-  </si>
-  <si>
-    <t>AVANRENREN FAVOUR OMOZUSI</t>
-  </si>
-  <si>
-    <t>OKOLI EBUKA EMMANUEL</t>
-  </si>
-  <si>
-    <t>OLAGUNJU ANDREW BOLUWATIFE</t>
-  </si>
-  <si>
-    <t>MAIKANO FAVOUR SHARON</t>
-  </si>
-  <si>
-    <t>THANNI ABDULMAJEED EKUNDAYO</t>
-  </si>
-  <si>
-    <t>SANNI SAMUEL OBANIJESU</t>
-  </si>
-  <si>
-    <t>OTASOWIE JOYCE IFEOLUWA</t>
-  </si>
-  <si>
-    <t>OGUNNIYI DEBORAH FOLAKEMI</t>
-  </si>
-  <si>
-    <t>QUADRI MARYAM OLUWAKEMI</t>
-  </si>
-  <si>
-    <t>OJORA ADIAT DEMILADE</t>
-  </si>
-  <si>
-    <t>OKHIKU DORCAS OMOYEME</t>
-  </si>
-  <si>
-    <t>BABALOLA, OLARONKE WASILAT</t>
-  </si>
-  <si>
-    <t>ADEBAMBO, OLUWASEUN ADURAGBEMI</t>
-  </si>
-  <si>
-    <t>ADENIRAN, MUHAMMAD ADEDAMOLA</t>
-  </si>
-  <si>
-    <t>FETUGA, MUSTAPHA</t>
-  </si>
-  <si>
-    <t>AJISAFE, OKIKIOLA GRACE</t>
-  </si>
-  <si>
-    <t>OFEM, MFAWAYOBASE PAULA</t>
-  </si>
-  <si>
-    <t>EBOKPO, ESTHER IJIBA</t>
-  </si>
-  <si>
-    <t>ONI, ESTHER OLUWAFERANMI</t>
-  </si>
-  <si>
-    <t>SURAJUDEEN, IBRAHIM OPEYEMI</t>
-  </si>
-  <si>
-    <t>AYODELE, BOLUWATIFE CLEMENT</t>
-  </si>
-  <si>
-    <t>ADESINA, EMMANUEL ADEWALE</t>
-  </si>
-  <si>
-    <t>MORANTI, OLUWATOBI IYANUOLUWA</t>
-  </si>
-  <si>
-    <t>ADESINA, JAMES OPEOLUWA</t>
-  </si>
-  <si>
-    <t>ALBERT, TEMITOPE ELIZABETH</t>
-  </si>
-  <si>
-    <t>OLOGUN, RUTH OLUWAPELUMI</t>
-  </si>
-  <si>
-    <t>MAMMAH, TEMISAN TOLULOPE</t>
-  </si>
-  <si>
-    <t>OYEWOLE, EGANMOSI OKIKIOLA</t>
-  </si>
-  <si>
-    <t>ADEBIYI, DAVID AYOMIPOSI</t>
-  </si>
-  <si>
-    <t>IDOWU, OREOLUWA OREOLUWA</t>
-  </si>
-  <si>
-    <t>EZEAMAKU, EMMANUELLA MUNACHIMSO</t>
-  </si>
-  <si>
-    <t>AYINDE, AKINMADE ELIZABETH</t>
-  </si>
-  <si>
-    <t>CLEMENT, PAUL IKHILE</t>
-  </si>
-  <si>
-    <t>OLOWOHUNWA, HEPHZIBAH OLUWATOYIN</t>
-  </si>
-  <si>
-    <t>OJEWUMI, IFEOLUWA ADESUWA</t>
-  </si>
-  <si>
-    <t>OGUNLESI, OLUWASEUN OLADIIPUPO</t>
-  </si>
-  <si>
-    <t>AKODU, ABDURRAHMAN</t>
-  </si>
-  <si>
-    <t>ECHETA, FAVOUR CHINENYE</t>
-  </si>
-  <si>
-    <t>OMOLE, OLUWAFEMI ABRAHAM</t>
-  </si>
-  <si>
-    <t>SALAMI, ADESHINA IFAKAYODE</t>
-  </si>
-  <si>
-    <t>ONIFADE, OPEOLUWA BISOLA</t>
-  </si>
-  <si>
-    <t>OGHENECHOJA, SHARON OREZIME</t>
-  </si>
-  <si>
-    <t>EDEM, EMEM GABRIEL</t>
-  </si>
-  <si>
-    <t>FADIPE, OLUWATUNMININU TITILOPE</t>
-  </si>
-  <si>
-    <t>BAMIBOYE, TEMITOPE AYOMIDE</t>
-  </si>
-  <si>
-    <t>OROPO, IRADAH MOTUNLADE</t>
-  </si>
-  <si>
-    <t>OPEIFA, OMOLOTO IBUKUNOLUWA</t>
-  </si>
-  <si>
-    <t>ADEEKO, ADEMIDARA OLUWATUNMISE</t>
-  </si>
-  <si>
-    <t>ADEBAYO, SUKURAT ADERAYO</t>
-  </si>
-  <si>
-    <t>Ntui, Samuel</t>
-  </si>
-  <si>
-    <t>Afonja Joanna Opeyemi</t>
-  </si>
-  <si>
-    <t>Odu Blessing  Okibe</t>
+    <t xml:space="preserve">Adeniyi Muinat Omobusayo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obiwulu God'swill Eric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teniola Eniola Naomi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raji Khairat Ayomide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adeyeye Folasade Blessing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opreh Victor Omoghene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bazuaye Peter Esosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obiwulu Josephine Amarachi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anoma Onyinyechukwu Daniella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gladstone Okechukwu Nnabue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Endurance Ehidiame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fred Virtue Utip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ofili Great Echendu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Okpani Victoria Enya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odu Blessing  Okibe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afonja Joanna Opeyemi</t>
   </si>
   <si>
     <t xml:space="preserve">Iortyom Sewuese Lois </t>
   </si>
   <si>
-    <t>Okpani Victoria Enya</t>
-  </si>
-  <si>
-    <t>Fred Virtue Utip</t>
+    <t xml:space="preserve">BABALOLA, OLARONKE WASILAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBANGA, ABASIONO NSIKANABASI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEBAMBO, OLUWASEUN ADURAGBEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADENIRAN, MUHAMMAD ADEDAMOLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FETUGA, MUSTAPHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJISAFE, OKIKIOLA GRACE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFEM, MFAWAYOBASE PAULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBOKPO, ESTHER IJIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONI, ESTHER OLUWAFERANMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SURAJUDEEN, IBRAHIM OPEYEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AYODELE, BOLUWATIFE CLEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADESINA, EMMANUEL ADEWALE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORANTI, OLUWATOBI IYANUOLUWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADESINA, JAMES OPEOLUWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALBERT, TEMITOPE ELIZABETH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLOGUN, RUTH OLUWAPELUMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAMMAH, TEMISAN TOLULOPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OYEWOLE, EGANMOSI OKIKIOLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEBIYI, DAVID AYOMIPOSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDOWU, OREOLUWA OREOLUWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAMAKU, EMMANUELLA MUNACHIMSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AYINDE, AKINMADE ELIZABETH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEMENT, PAUL IKHILE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLOWOHUNWA, HEPHZIBAH OLUWATOYIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OJEWUMI, IFEOLUWA ADESUWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGUNLESI, OLUWASEUN OLADIIPUPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKODU, ABDURRAHMAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHETA, FAVOUR CHINENYE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOLE, OLUWAFEMI ABRAHAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALAMI, ADESHINA IFAKAYODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONIFADE, OPEOLUWA BISOLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGHENECHOJA, SHARON OREZIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDEM, EMEM GABRIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FADIPE, OLUWATUNMININU TITILOPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAMIBOYE, TEMITOPE AYOMIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OROPO, IRADAH MOTUNLADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEIFA, OMOLOTO IBUKUNOLUWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEEKO, ADEMIDARA OLUWATUNMISE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEBAYO, SUKURAT ADERAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adigwu, Judith Ogechukwu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ago, Henry Boniface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajekwe, Elizabeth Yaveren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akin-ologunowa, Oluwadamilola Peace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akomaye, Emmanuella Agiounim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asuquo, Deborah Asuquo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awafung, Rosemary Odey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyo, Gideon Edet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ntui, Samuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owolabi, Confidence Tolulope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANIGBEDU EVIDENCE DAVID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALUMMA CHIDERA JESSICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICHOLAS NAOMI BLESSING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKHIGBE OSIREGBEMHE EMMANUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBITOYE TIMILEHIN ISRAEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKUYIGA ADEDAYO OLUWAROTIMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVANRENREN FAVOUR OMOZUSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKOLI EBUKA EMMANUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLAGUNJU ANDREW BOLUWATIFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIKANO FAVOUR SHARON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THANNI ABDULMAJEED EKUNDAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANNI SAMUEL OBANIJESU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTASOWIE JOYCE IFEOLUWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGUNNIYI DEBORAH FOLAKEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUADRI MARYAM OLUWAKEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OJORA ADIAT DEMILADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKHIKU DORCAS OMOYEME</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -646,18 +637,18 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,8 +666,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -718,74 +992,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -793,7 +1007,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -819,7 +1033,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -871,16 +1085,28 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -896,7 +1122,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -927,28 +1153,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:D206"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="10"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="37.21875"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="15.33203125"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="37.44140625"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="31.77734375"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -962,7 +1181,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -976,7 +1195,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -990,7 +1209,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1004,7 +1223,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1018,7 +1237,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1032,7 +1251,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1046,7 +1265,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1060,7 +1279,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1074,7 +1293,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1088,7 +1307,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1102,7 +1321,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1116,7 +1335,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1130,7 +1349,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1144,7 +1363,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1158,7 +1377,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1172,7 +1391,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1186,7 +1405,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1200,7 +1419,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1214,7 +1433,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1228,7 +1447,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1242,7 +1461,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1256,7 +1475,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1270,7 +1489,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1284,7 +1503,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1298,7 +1517,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1312,7 +1531,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1326,7 +1545,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1340,7 +1559,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1354,7 +1573,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1368,7 +1587,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1382,7 +1601,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1396,7 +1615,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1410,7 +1629,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1424,7 +1643,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1438,7 +1657,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1452,7 +1671,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1466,7 +1685,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1480,7 +1699,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1494,7 +1713,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1508,7 +1727,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1522,20 +1741,20 @@
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43">
       <c r="C43" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="C44" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45">
       <c r="A45">
         <v>1</v>
       </c>
@@ -1543,13 +1762,13 @@
         <v>230701002</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D45">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46">
       <c r="A46">
         <v>2</v>
       </c>
@@ -1557,13 +1776,13 @@
         <v>230701003</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D46">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47">
       <c r="A47">
         <v>3</v>
       </c>
@@ -1571,13 +1790,13 @@
         <v>230701004</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D47">
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48">
       <c r="A48">
         <v>4</v>
       </c>
@@ -1585,27 +1804,27 @@
         <v>230301005</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D48">
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49">
       <c r="A49">
         <v>5</v>
       </c>
       <c r="B49">
-        <v>230701005</v>
+        <v>230701006</v>
       </c>
       <c r="C49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D49">
         <v>300</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50">
       <c r="A50">
         <v>6</v>
       </c>
@@ -1613,13 +1832,13 @@
         <v>230701007</v>
       </c>
       <c r="C50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D50">
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51">
       <c r="A51">
         <v>7</v>
       </c>
@@ -1627,13 +1846,13 @@
         <v>230701008</v>
       </c>
       <c r="C51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D51">
         <v>300</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52">
       <c r="A52">
         <v>8</v>
       </c>
@@ -1641,13 +1860,13 @@
         <v>230701009</v>
       </c>
       <c r="C52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D52">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53">
       <c r="A53">
         <v>9</v>
       </c>
@@ -1655,13 +1874,13 @@
         <v>230701010</v>
       </c>
       <c r="C53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D53">
         <v>300</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54">
       <c r="A54">
         <v>10</v>
       </c>
@@ -1669,13 +1888,13 @@
         <v>230701011</v>
       </c>
       <c r="C54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D54">
         <v>300</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55">
       <c r="A55">
         <v>11</v>
       </c>
@@ -1683,13 +1902,13 @@
         <v>230701012</v>
       </c>
       <c r="C55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D55">
         <v>300</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56">
       <c r="A56">
         <v>12</v>
       </c>
@@ -1697,13 +1916,13 @@
         <v>230701013</v>
       </c>
       <c r="C56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D56">
         <v>300</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57">
       <c r="A57">
         <v>13</v>
       </c>
@@ -1711,13 +1930,13 @@
         <v>230701014</v>
       </c>
       <c r="C57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D57">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58">
       <c r="A58">
         <v>14</v>
       </c>
@@ -1725,13 +1944,13 @@
         <v>230701015</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D58">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59">
       <c r="A59">
         <v>15</v>
       </c>
@@ -1739,13 +1958,13 @@
         <v>230701016</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D59">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60">
       <c r="A60">
         <v>16</v>
       </c>
@@ -1753,13 +1972,13 @@
         <v>230701017</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D60">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61">
       <c r="A61">
         <v>17</v>
       </c>
@@ -1767,13 +1986,13 @@
         <v>230701018</v>
       </c>
       <c r="C61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D61">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62">
       <c r="A62">
         <v>18</v>
       </c>
@@ -1781,13 +2000,13 @@
         <v>230701019</v>
       </c>
       <c r="C62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D62">
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63">
       <c r="A63">
         <v>19</v>
       </c>
@@ -1795,13 +2014,13 @@
         <v>230701020</v>
       </c>
       <c r="C63" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D63">
         <v>300</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64">
       <c r="A64">
         <v>20</v>
       </c>
@@ -1809,13 +2028,13 @@
         <v>230701021</v>
       </c>
       <c r="C64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D64">
         <v>300</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65">
       <c r="A65">
         <v>21</v>
       </c>
@@ -1823,13 +2042,13 @@
         <v>230701022</v>
       </c>
       <c r="C65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D65">
         <v>300</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66">
       <c r="A66">
         <v>22</v>
       </c>
@@ -1837,13 +2056,13 @@
         <v>230701023</v>
       </c>
       <c r="C66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D66">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67">
       <c r="A67">
         <v>23</v>
       </c>
@@ -1851,13 +2070,13 @@
         <v>230701024</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D67">
         <v>300</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68">
       <c r="A68">
         <v>24</v>
       </c>
@@ -1865,13 +2084,13 @@
         <v>230701025</v>
       </c>
       <c r="C68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D68">
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69">
       <c r="A69">
         <v>25</v>
       </c>
@@ -1879,13 +2098,13 @@
         <v>230701026</v>
       </c>
       <c r="C69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D69">
         <v>300</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70">
       <c r="A70">
         <v>26</v>
       </c>
@@ -1893,13 +2112,13 @@
         <v>230701027</v>
       </c>
       <c r="C70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D70">
         <v>300</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71">
       <c r="A71">
         <v>27</v>
       </c>
@@ -1907,13 +2126,13 @@
         <v>230701028</v>
       </c>
       <c r="C71" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D71">
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72">
       <c r="A72">
         <v>28</v>
       </c>
@@ -1921,13 +2140,13 @@
         <v>230701029</v>
       </c>
       <c r="C72" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D72">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73">
       <c r="A73">
         <v>29</v>
       </c>
@@ -1935,13 +2154,13 @@
         <v>240701501</v>
       </c>
       <c r="C73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D73">
         <v>300</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74">
       <c r="A74">
         <v>30</v>
       </c>
@@ -1949,13 +2168,13 @@
         <v>240701502</v>
       </c>
       <c r="C74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D74">
         <v>300</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75">
       <c r="A75">
         <v>31</v>
       </c>
@@ -1963,13 +2182,13 @@
         <v>240701503</v>
       </c>
       <c r="C75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D75">
         <v>300</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76">
       <c r="A76">
         <v>32</v>
       </c>
@@ -1977,13 +2196,13 @@
         <v>240701504</v>
       </c>
       <c r="C76" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D76">
         <v>300</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77">
       <c r="A77">
         <v>33</v>
       </c>
@@ -1991,13 +2210,13 @@
         <v>240701505</v>
       </c>
       <c r="C77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D77">
         <v>300</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78">
       <c r="A78">
         <v>34</v>
       </c>
@@ -2005,13 +2224,13 @@
         <v>240701506</v>
       </c>
       <c r="C78" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D78">
         <v>300</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79">
       <c r="A79">
         <v>35</v>
       </c>
@@ -2019,13 +2238,13 @@
         <v>240701507</v>
       </c>
       <c r="C79" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D79">
         <v>300</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80">
       <c r="A80">
         <v>36</v>
       </c>
@@ -2033,13 +2252,13 @@
         <v>240701508</v>
       </c>
       <c r="C80" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D80">
         <v>300</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81">
       <c r="A81">
         <v>37</v>
       </c>
@@ -2047,13 +2266,13 @@
         <v>240701509</v>
       </c>
       <c r="C81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D81">
         <v>300</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82">
       <c r="A82">
         <v>38</v>
       </c>
@@ -2061,13 +2280,13 @@
         <v>240701510</v>
       </c>
       <c r="C82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D82">
         <v>300</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83">
       <c r="A83">
         <v>39</v>
       </c>
@@ -2075,13 +2294,13 @@
         <v>240701511</v>
       </c>
       <c r="C83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D83">
         <v>300</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84">
       <c r="A84">
         <v>40</v>
       </c>
@@ -2089,13 +2308,13 @@
         <v>240701512</v>
       </c>
       <c r="C84" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D84">
         <v>300</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85">
       <c r="A85">
         <v>41</v>
       </c>
@@ -2103,13 +2322,13 @@
         <v>240701513</v>
       </c>
       <c r="C85" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D85">
         <v>300</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86">
       <c r="A86">
         <v>42</v>
       </c>
@@ -2117,13 +2336,13 @@
         <v>240708544</v>
       </c>
       <c r="C86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D86">
         <v>300</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89">
       <c r="A89">
         <v>1</v>
       </c>
@@ -2137,7 +2356,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90">
       <c r="A90">
         <v>2</v>
       </c>
@@ -2151,7 +2370,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91">
       <c r="A91">
         <v>3</v>
       </c>
@@ -2165,7 +2384,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92">
       <c r="A92">
         <v>4</v>
       </c>
@@ -2179,7 +2398,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93">
       <c r="A93">
         <v>5</v>
       </c>
@@ -2193,7 +2412,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94">
       <c r="A94">
         <v>6</v>
       </c>
@@ -2207,7 +2426,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95">
       <c r="A95">
         <v>7</v>
       </c>
@@ -2221,7 +2440,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96">
       <c r="A96">
         <v>8</v>
       </c>
@@ -2235,7 +2454,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97">
       <c r="A97">
         <v>9</v>
       </c>
@@ -2249,7 +2468,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98">
       <c r="A98">
         <v>10</v>
       </c>
@@ -2263,7 +2482,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99">
       <c r="A99">
         <v>11</v>
       </c>
@@ -2277,7 +2496,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100">
       <c r="A100">
         <v>12</v>
       </c>
@@ -2291,7 +2510,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101">
       <c r="A101">
         <v>13</v>
       </c>
@@ -2305,7 +2524,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102">
       <c r="A102">
         <v>14</v>
       </c>
@@ -2319,7 +2538,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103">
       <c r="A103">
         <v>15</v>
       </c>
@@ -2333,7 +2552,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104">
       <c r="A104">
         <v>16</v>
       </c>
@@ -2347,7 +2566,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105">
       <c r="A105">
         <v>17</v>
       </c>
@@ -2361,7 +2580,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106">
       <c r="A106">
         <v>18</v>
       </c>
@@ -2375,7 +2594,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107">
       <c r="A107">
         <v>19</v>
       </c>
@@ -2389,7 +2608,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108">
       <c r="A108">
         <v>20</v>
       </c>
@@ -2403,7 +2622,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109">
       <c r="A109">
         <v>21</v>
       </c>
@@ -2417,7 +2636,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110">
       <c r="A110">
         <v>22</v>
       </c>
@@ -2431,7 +2650,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111">
       <c r="A111">
         <v>23</v>
       </c>
@@ -2445,7 +2664,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112">
       <c r="A112">
         <v>24</v>
       </c>
@@ -2459,7 +2678,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113">
       <c r="A113">
         <v>25</v>
       </c>
@@ -2473,7 +2692,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114">
       <c r="A114">
         <v>26</v>
       </c>
@@ -2487,7 +2706,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115">
       <c r="A115">
         <v>27</v>
       </c>
@@ -2501,7 +2720,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116">
       <c r="A116">
         <v>28</v>
       </c>
@@ -2515,7 +2734,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117">
       <c r="A117">
         <v>29</v>
       </c>
@@ -2529,7 +2748,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118">
       <c r="A118">
         <v>30</v>
       </c>
@@ -2543,7 +2762,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119">
       <c r="A119">
         <v>31</v>
       </c>
@@ -2557,7 +2776,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120">
       <c r="A120">
         <v>32</v>
       </c>
@@ -2571,7 +2790,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121">
       <c r="A121">
         <v>33</v>
       </c>
@@ -2585,7 +2804,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122">
       <c r="A122">
         <v>34</v>
       </c>
@@ -2599,7 +2818,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123">
       <c r="A123">
         <v>35</v>
       </c>
@@ -2613,7 +2832,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124">
       <c r="A124">
         <v>36</v>
       </c>
@@ -2627,7 +2846,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125">
       <c r="A125">
         <v>37</v>
       </c>
@@ -2641,7 +2860,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126">
       <c r="A126">
         <v>38</v>
       </c>
@@ -2655,7 +2874,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127">
       <c r="A127">
         <v>39</v>
       </c>
@@ -2669,7 +2888,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128">
       <c r="A128">
         <v>40</v>
       </c>
@@ -2683,7 +2902,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129">
       <c r="A129">
         <v>41</v>
       </c>
@@ -2697,7 +2916,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130">
       <c r="A130">
         <v>42</v>
       </c>
@@ -2711,7 +2930,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131">
       <c r="A131">
         <v>43</v>
       </c>
@@ -2719,13 +2938,13 @@
         <v>250701139</v>
       </c>
       <c r="C131" t="s">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="D131">
         <v>400</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132">
       <c r="A132">
         <v>44</v>
       </c>
@@ -2733,13 +2952,13 @@
         <v>250701146</v>
       </c>
       <c r="C132" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D132">
         <v>400</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133">
       <c r="A133">
         <v>45</v>
       </c>
@@ -2747,13 +2966,13 @@
         <v>250701140</v>
       </c>
       <c r="C133" t="s">
-        <v>197</v>
+        <v>129</v>
       </c>
       <c r="D133">
         <v>400</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134">
       <c r="A134">
         <v>46</v>
       </c>
@@ -2761,13 +2980,13 @@
         <v>250701150</v>
       </c>
       <c r="C134" t="s">
-        <v>195</v>
+        <v>130</v>
       </c>
       <c r="D134">
         <v>400</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135">
       <c r="A135">
         <v>47</v>
       </c>
@@ -2775,13 +2994,13 @@
         <v>250701138</v>
       </c>
       <c r="C135" t="s">
-        <v>194</v>
+        <v>131</v>
       </c>
       <c r="D135">
         <v>400</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136">
       <c r="A136">
         <v>48</v>
       </c>
@@ -2789,13 +3008,13 @@
         <v>250701141</v>
       </c>
       <c r="C136" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="D136">
         <v>400</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139">
       <c r="A139">
         <v>1</v>
       </c>
@@ -2803,13 +3022,13 @@
         <v>170314100</v>
       </c>
       <c r="C139" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="D139">
         <v>500</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140">
       <c r="A140">
         <v>2</v>
       </c>
@@ -2817,13 +3036,13 @@
         <v>180705082</v>
       </c>
       <c r="C140" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D140">
         <v>500</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141">
       <c r="A141">
         <v>3</v>
       </c>
@@ -2831,13 +3050,13 @@
         <v>190701001</v>
       </c>
       <c r="C141" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D141">
         <v>500</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142">
       <c r="A142">
         <v>4</v>
       </c>
@@ -2845,13 +3064,13 @@
         <v>190701002</v>
       </c>
       <c r="C142" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D142">
         <v>500</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143">
       <c r="A143">
         <v>5</v>
       </c>
@@ -2859,13 +3078,13 @@
         <v>190701003</v>
       </c>
       <c r="C143" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D143">
         <v>500</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144">
       <c r="A144">
         <v>6</v>
       </c>
@@ -2873,13 +3092,13 @@
         <v>190701004</v>
       </c>
       <c r="C144" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D144">
         <v>500</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145">
       <c r="A145">
         <v>7</v>
       </c>
@@ -2887,13 +3106,13 @@
         <v>190701005</v>
       </c>
       <c r="C145" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D145">
         <v>500</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146">
       <c r="A146">
         <v>8</v>
       </c>
@@ -2901,13 +3120,13 @@
         <v>190701006</v>
       </c>
       <c r="C146" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="D146">
         <v>500</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147">
       <c r="A147">
         <v>9</v>
       </c>
@@ -2915,13 +3134,13 @@
         <v>190701007</v>
       </c>
       <c r="C147" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="D147">
         <v>500</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148">
       <c r="A148">
         <v>10</v>
       </c>
@@ -2929,13 +3148,13 @@
         <v>190701008</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D148">
         <v>500</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149">
       <c r="A149">
         <v>11</v>
       </c>
@@ -2943,13 +3162,13 @@
         <v>190701011</v>
       </c>
       <c r="C149" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D149">
         <v>500</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150">
       <c r="A150">
         <v>13</v>
       </c>
@@ -2957,13 +3176,13 @@
         <v>190701012</v>
       </c>
       <c r="C150" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D150">
         <v>500</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151">
       <c r="A151">
         <v>13</v>
       </c>
@@ -2971,13 +3190,13 @@
         <v>190701014</v>
       </c>
       <c r="C151" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D151">
         <v>500</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152">
       <c r="A152">
         <v>15</v>
       </c>
@@ -2985,13 +3204,13 @@
         <v>190701015</v>
       </c>
       <c r="C152" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="D152">
         <v>500</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153">
       <c r="A153">
         <v>15</v>
       </c>
@@ -2999,13 +3218,13 @@
         <v>190701016</v>
       </c>
       <c r="C153" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D153">
         <v>500</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154">
       <c r="A154">
         <v>16</v>
       </c>
@@ -3013,13 +3232,13 @@
         <v>190701017</v>
       </c>
       <c r="C154" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D154">
         <v>500</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155">
       <c r="A155">
         <v>17</v>
       </c>
@@ -3027,13 +3246,13 @@
         <v>190701019</v>
       </c>
       <c r="C155" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D155">
         <v>500</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156">
       <c r="A156">
         <v>18</v>
       </c>
@@ -3041,13 +3260,13 @@
         <v>190701021</v>
       </c>
       <c r="C156" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="D156">
         <v>500</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157">
       <c r="A157">
         <v>19</v>
       </c>
@@ -3055,13 +3274,13 @@
         <v>190701023</v>
       </c>
       <c r="C157" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="D157">
         <v>500</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158">
       <c r="A158">
         <v>20</v>
       </c>
@@ -3069,13 +3288,13 @@
         <v>190701025</v>
       </c>
       <c r="C158" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D158">
         <v>500</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159">
       <c r="A159">
         <v>21</v>
       </c>
@@ -3083,13 +3302,13 @@
         <v>190701026</v>
       </c>
       <c r="C159" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D159">
         <v>500</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160">
       <c r="A160">
         <v>22</v>
       </c>
@@ -3097,13 +3316,13 @@
         <v>190701028</v>
       </c>
       <c r="C160" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D160">
         <v>500</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161">
       <c r="A161">
         <v>23</v>
       </c>
@@ -3111,13 +3330,13 @@
         <v>190701029</v>
       </c>
       <c r="C161" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="D161">
         <v>500</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162">
       <c r="A162">
         <v>24</v>
       </c>
@@ -3125,13 +3344,13 @@
         <v>190701031</v>
       </c>
       <c r="C162" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="D162">
         <v>500</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163">
       <c r="A163">
         <v>25</v>
       </c>
@@ -3139,13 +3358,13 @@
         <v>190701032</v>
       </c>
       <c r="C163" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D163">
         <v>500</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164">
       <c r="A164">
         <v>26</v>
       </c>
@@ -3153,13 +3372,13 @@
         <v>190701034</v>
       </c>
       <c r="C164" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="D164">
         <v>500</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165">
       <c r="A165">
         <v>27</v>
       </c>
@@ -3167,13 +3386,13 @@
         <v>190705137</v>
       </c>
       <c r="C165" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="D165">
         <v>500</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166">
       <c r="A166">
         <v>28</v>
       </c>
@@ -3181,13 +3400,13 @@
         <v>210701501</v>
       </c>
       <c r="C166" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="D166">
         <v>500</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167">
       <c r="A167">
         <v>29</v>
       </c>
@@ -3195,13 +3414,13 @@
         <v>210701502</v>
       </c>
       <c r="C167" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="D167">
         <v>500</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168">
       <c r="A168">
         <v>30</v>
       </c>
@@ -3209,13 +3428,13 @@
         <v>210701503</v>
       </c>
       <c r="C168" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="D168">
         <v>500</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169">
       <c r="A169">
         <v>31</v>
       </c>
@@ -3223,13 +3442,13 @@
         <v>210701504</v>
       </c>
       <c r="C169" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="D169">
         <v>500</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170">
       <c r="A170">
         <v>32</v>
       </c>
@@ -3237,13 +3456,13 @@
         <v>210701505</v>
       </c>
       <c r="C170" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="D170">
         <v>500</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171">
       <c r="A171">
         <v>33</v>
       </c>
@@ -3251,13 +3470,13 @@
         <v>210701506</v>
       </c>
       <c r="C171" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="D171">
         <v>500</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172">
       <c r="A172">
         <v>34</v>
       </c>
@@ -3265,13 +3484,13 @@
         <v>210701507</v>
       </c>
       <c r="C172" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="D172">
         <v>500</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173">
       <c r="A173">
         <v>35</v>
       </c>
@@ -3279,13 +3498,13 @@
         <v>210701508</v>
       </c>
       <c r="C173" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="D173">
         <v>500</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174">
       <c r="A174">
         <v>36</v>
       </c>
@@ -3293,13 +3512,13 @@
         <v>210701509</v>
       </c>
       <c r="C174" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="D174">
         <v>500</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175">
       <c r="A175">
         <v>37</v>
       </c>
@@ -3307,13 +3526,13 @@
         <v>210701510</v>
       </c>
       <c r="C175" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="D175">
         <v>500</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176">
       <c r="A176">
         <v>38</v>
       </c>
@@ -3321,13 +3540,13 @@
         <v>210701511</v>
       </c>
       <c r="C176" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="D176">
         <v>500</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177">
       <c r="A177">
         <v>39</v>
       </c>
@@ -3335,13 +3554,13 @@
         <v>210701512</v>
       </c>
       <c r="C177" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D177">
         <v>500</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178">
       <c r="A178">
         <v>40</v>
       </c>
@@ -3349,13 +3568,13 @@
         <v>250701147</v>
       </c>
       <c r="C178" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="D178">
         <v>500</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179">
       <c r="A179">
         <v>41</v>
       </c>
@@ -3363,13 +3582,13 @@
         <v>250701151</v>
       </c>
       <c r="C179" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="D179">
         <v>500</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180">
       <c r="A180">
         <v>42</v>
       </c>
@@ -3377,13 +3596,13 @@
         <v>250701148</v>
       </c>
       <c r="C180" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="D180">
         <v>500</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181">
       <c r="A181">
         <v>43</v>
       </c>
@@ -3391,13 +3610,13 @@
         <v>250701145</v>
       </c>
       <c r="C181" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="D181">
         <v>500</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182">
       <c r="A182">
         <v>44</v>
       </c>
@@ -3405,13 +3624,13 @@
         <v>250701144</v>
       </c>
       <c r="C182" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="D182">
         <v>500</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183">
       <c r="A183">
         <v>45</v>
       </c>
@@ -3419,13 +3638,13 @@
         <v>250701149</v>
       </c>
       <c r="C183" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="D183">
         <v>500</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184">
       <c r="A184">
         <v>46</v>
       </c>
@@ -3433,13 +3652,13 @@
         <v>250701152</v>
       </c>
       <c r="C184" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="D184">
         <v>500</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185">
       <c r="A185">
         <v>47</v>
       </c>
@@ -3447,13 +3666,13 @@
         <v>250701143</v>
       </c>
       <c r="C185" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="D185">
         <v>500</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186">
       <c r="A186">
         <v>48</v>
       </c>
@@ -3461,13 +3680,13 @@
         <v>250701142</v>
       </c>
       <c r="C186" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D186">
         <v>500</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187">
       <c r="A187">
         <v>49</v>
       </c>
@@ -3475,13 +3694,13 @@
         <v>250701153</v>
       </c>
       <c r="C187" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="D187">
         <v>500</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190">
       <c r="A190">
         <v>1</v>
       </c>
@@ -3489,13 +3708,13 @@
         <v>170701015</v>
       </c>
       <c r="C190" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="D190">
         <v>600</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191">
       <c r="A191">
         <v>2</v>
       </c>
@@ -3503,13 +3722,13 @@
         <v>180705028</v>
       </c>
       <c r="C191" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="D191">
         <v>600</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192">
       <c r="A192">
         <v>3</v>
       </c>
@@ -3517,13 +3736,13 @@
         <v>180705045</v>
       </c>
       <c r="C192" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="D192">
         <v>600</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193">
       <c r="A193">
         <v>4</v>
       </c>
@@ -3531,13 +3750,13 @@
         <v>190701504</v>
       </c>
       <c r="C193" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="D193">
         <v>600</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194">
       <c r="A194">
         <v>5</v>
       </c>
@@ -3545,13 +3764,13 @@
         <v>190701502</v>
       </c>
       <c r="C194" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="D194">
         <v>600</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195">
       <c r="A195">
         <v>6</v>
       </c>
@@ -3559,13 +3778,13 @@
         <v>190701501</v>
       </c>
       <c r="C195" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="D195">
         <v>600</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196">
       <c r="A196">
         <v>7</v>
       </c>
@@ -3573,13 +3792,13 @@
         <v>190701506</v>
       </c>
       <c r="C196" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="D196">
         <v>600</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197">
       <c r="A197">
         <v>8</v>
       </c>
@@ -3587,13 +3806,13 @@
         <v>190701507</v>
       </c>
       <c r="C197" t="s">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="D197">
         <v>600</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198">
       <c r="A198">
         <v>9</v>
       </c>
@@ -3601,13 +3820,13 @@
         <v>180705019</v>
       </c>
       <c r="C198" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="D198">
         <v>600</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199">
       <c r="A199">
         <v>10</v>
       </c>
@@ -3615,13 +3834,13 @@
         <v>180705054</v>
       </c>
       <c r="C199" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="D199">
         <v>600</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200">
       <c r="A200">
         <v>11</v>
       </c>
@@ -3629,13 +3848,13 @@
         <v>180705057</v>
       </c>
       <c r="C200" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="D200">
         <v>600</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201">
       <c r="A201">
         <v>12</v>
       </c>
@@ -3643,13 +3862,13 @@
         <v>180705071</v>
       </c>
       <c r="C201" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="D201">
         <v>600</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202">
       <c r="A202">
         <v>13</v>
       </c>
@@ -3657,13 +3876,13 @@
         <v>180705074</v>
       </c>
       <c r="C202" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="D202">
         <v>600</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203">
       <c r="A203">
         <v>14</v>
       </c>
@@ -3671,13 +3890,13 @@
         <v>180705075</v>
       </c>
       <c r="C203" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="D203">
         <v>600</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204">
       <c r="A204">
         <v>15</v>
       </c>
@@ -3685,13 +3904,13 @@
         <v>180705077</v>
       </c>
       <c r="C204" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="D204">
         <v>600</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205">
       <c r="A205">
         <v>16</v>
       </c>
@@ -3699,13 +3918,13 @@
         <v>180705079</v>
       </c>
       <c r="C205" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="D205">
         <v>600</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206">
       <c r="A206">
         <v>17</v>
       </c>
@@ -3713,13 +3932,16 @@
         <v>180705080</v>
       </c>
       <c r="C206" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="D206">
         <v>600</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>